--- a/seminar_03/problem_4.15_solution.xlsx
+++ b/seminar_03/problem_4.15_solution.xlsx
@@ -2198,9 +2198,10 @@
         <f>FINV(0.05,B7,B8)</f>
         <v/>
       </c>
-      <c r="C10" s="25">
-        <f>FРАСПОБР(0,05; q; n − k)</f>
-        <v/>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>=FРАСПОБР(0,05; q; n − k)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2213,9 +2214,10 @@
         <f>FDIST(B9,B7,B8)</f>
         <v/>
       </c>
-      <c r="C11" s="25">
-        <f>FРАСП(F; q; n − k)</f>
-        <v/>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>=FРАСП(F; q; n − k)</t>
+        </is>
       </c>
     </row>
     <row r="12">
